--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5cbc24d1a217bff/Poker/Bankroll/stang-gang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{057D2BFF-A66A-4CE6-AAFA-6D0F7FCF26FD}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C562163-879E-4A92-B1F8-DD1AF1B79CB1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Date</t>
   </si>
@@ -45,18 +45,6 @@
   </si>
   <si>
     <t>The Micros</t>
-  </si>
-  <si>
-    <t>Total Hands</t>
-  </si>
-  <si>
-    <t>NL100</t>
-  </si>
-  <si>
-    <t>NL40</t>
-  </si>
-  <si>
-    <t>Stake</t>
   </si>
 </sst>
 </file>
@@ -433,13 +421,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A52CD65-A2BF-4AC2-8075-EA939B042110}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,14 +437,8 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45967</v>
       </c>
@@ -466,22 +448,16 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45968</v>
       </c>
       <c r="C3">
         <v>-20</v>
       </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45975</v>
       </c>
@@ -491,372 +467,488 @@
       <c r="C4">
         <v>230</v>
       </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45981</v>
       </c>
       <c r="C5">
         <v>60</v>
       </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45984</v>
       </c>
       <c r="C6">
         <v>260</v>
       </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45985</v>
       </c>
       <c r="C7">
         <v>223</v>
       </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45986</v>
       </c>
       <c r="C8">
         <v>73</v>
       </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45992</v>
       </c>
       <c r="C9">
         <v>53</v>
       </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45993</v>
       </c>
       <c r="C10">
         <v>151</v>
       </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45994</v>
       </c>
       <c r="C11">
         <v>229</v>
       </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45995</v>
       </c>
       <c r="C12">
         <v>224</v>
       </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45996</v>
       </c>
       <c r="C13">
         <v>194</v>
       </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45997</v>
       </c>
       <c r="C14">
         <v>309</v>
       </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45998</v>
       </c>
       <c r="C15">
         <v>282</v>
       </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45999</v>
       </c>
       <c r="C16">
         <v>275</v>
       </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46000</v>
       </c>
       <c r="C17">
         <v>391</v>
       </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46001</v>
       </c>
       <c r="C18">
         <v>228</v>
       </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46002</v>
       </c>
       <c r="C19">
         <v>487</v>
       </c>
-      <c r="D19">
-        <v>5000</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46003</v>
       </c>
       <c r="C20">
         <v>583</v>
       </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46004</v>
       </c>
       <c r="C21">
         <v>648</v>
       </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46005</v>
       </c>
       <c r="C22">
         <v>755</v>
       </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46013</v>
       </c>
       <c r="C23">
         <v>925</v>
       </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46033</v>
       </c>
       <c r="C24">
         <v>750</v>
       </c>
-      <c r="D24">
-        <v>10000</v>
-      </c>
-      <c r="E24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46042</v>
       </c>
       <c r="C25">
         <v>450</v>
       </c>
-      <c r="E25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46050</v>
       </c>
       <c r="C26">
         <v>844</v>
       </c>
-      <c r="E26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46052</v>
       </c>
       <c r="C27">
         <v>1088</v>
       </c>
-      <c r="E27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46054</v>
       </c>
       <c r="C28">
         <v>987</v>
       </c>
-      <c r="E28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46055</v>
       </c>
       <c r="C29">
         <v>697</v>
       </c>
-      <c r="D29">
-        <v>15000</v>
-      </c>
-      <c r="E29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46056</v>
       </c>
       <c r="C30">
         <v>825</v>
       </c>
-      <c r="E30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46057</v>
       </c>
       <c r="C31">
         <v>929</v>
       </c>
-      <c r="E31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46058</v>
       </c>
       <c r="C32">
         <v>903</v>
       </c>
-      <c r="E32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46059</v>
       </c>
       <c r="C33">
         <v>1526</v>
       </c>
-      <c r="E33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46060</v>
       </c>
       <c r="C34">
         <v>1767</v>
       </c>
-      <c r="E34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46061</v>
       </c>
       <c r="C35">
         <v>1852</v>
       </c>
-      <c r="E35" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46062</v>
       </c>
-      <c r="B36">
-        <v>1000</v>
-      </c>
       <c r="C36">
         <v>2266</v>
       </c>
-      <c r="E36" t="s">
-        <v>4</v>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>46063</v>
+      </c>
+      <c r="C37">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>46065</v>
+      </c>
+      <c r="C38">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>46066</v>
+      </c>
+      <c r="C39">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>46068</v>
+      </c>
+      <c r="C40">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>46069</v>
+      </c>
+      <c r="C41">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>46070</v>
+      </c>
+      <c r="C42">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>46071</v>
+      </c>
+      <c r="C43">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>46072</v>
+      </c>
+      <c r="C44">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>46073</v>
+      </c>
+      <c r="C45">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>46075</v>
+      </c>
+      <c r="C46">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C47">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C48">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C49">
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C50">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C51">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C52">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C53">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C54">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C55">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C56">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C57">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C58">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>46089</v>
+      </c>
+      <c r="C59">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>46089</v>
+      </c>
+      <c r="C60">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C61">
+        <v>3406</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C62">
+        <v>3638</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C63">
+        <v>3727</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B64">
+        <v>1010</v>
+      </c>
+      <c r="C64">
+        <v>3702</v>
       </c>
     </row>
   </sheetData>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5cbc24d1a217bff/Poker/Bankroll/stang-gang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C562163-879E-4A92-B1F8-DD1AF1B79CB1}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FF460D1-3C78-41D7-BAF1-E4C659C50073}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
+    <workbookView xWindow="4668" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -721,7 +721,7 @@
         <v>46062</v>
       </c>
       <c r="C36">
-        <v>2266</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -729,7 +729,7 @@
         <v>46063</v>
       </c>
       <c r="C37">
-        <v>2562</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -737,7 +737,7 @@
         <v>46065</v>
       </c>
       <c r="C38">
-        <v>2605</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -745,7 +745,7 @@
         <v>46066</v>
       </c>
       <c r="C39">
-        <v>2773</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -753,7 +753,7 @@
         <v>46068</v>
       </c>
       <c r="C40">
-        <v>2555</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -761,7 +761,7 @@
         <v>46069</v>
       </c>
       <c r="C41">
-        <v>2506</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -769,7 +769,7 @@
         <v>46070</v>
       </c>
       <c r="C42">
-        <v>2645</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -777,7 +777,7 @@
         <v>46071</v>
       </c>
       <c r="C43">
-        <v>2831</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -785,7 +785,7 @@
         <v>46072</v>
       </c>
       <c r="C44">
-        <v>2760</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -793,7 +793,7 @@
         <v>46073</v>
       </c>
       <c r="C45">
-        <v>2590</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -801,7 +801,7 @@
         <v>46075</v>
       </c>
       <c r="C46">
-        <v>2367</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -809,7 +809,7 @@
         <v>46076</v>
       </c>
       <c r="C47">
-        <v>2660</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -817,7 +817,7 @@
         <v>46077</v>
       </c>
       <c r="C48">
-        <v>2682</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -825,7 +825,7 @@
         <v>46078</v>
       </c>
       <c r="C49">
-        <v>3096</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -833,7 +833,7 @@
         <v>46079</v>
       </c>
       <c r="C50">
-        <v>3092</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -841,7 +841,7 @@
         <v>46080</v>
       </c>
       <c r="C51">
-        <v>3127</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -849,7 +849,7 @@
         <v>46082</v>
       </c>
       <c r="C52">
-        <v>2845</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -857,7 +857,7 @@
         <v>46083</v>
       </c>
       <c r="C53">
-        <v>2679</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -865,7 +865,7 @@
         <v>46084</v>
       </c>
       <c r="C54">
-        <v>2530</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -873,7 +873,7 @@
         <v>46085</v>
       </c>
       <c r="C55">
-        <v>2370</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -881,7 +881,7 @@
         <v>46086</v>
       </c>
       <c r="C56">
-        <v>2602</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -889,7 +889,7 @@
         <v>46087</v>
       </c>
       <c r="C57">
-        <v>2546</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -897,7 +897,7 @@
         <v>46088</v>
       </c>
       <c r="C58">
-        <v>2858</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -905,7 +905,7 @@
         <v>46089</v>
       </c>
       <c r="C59">
-        <v>3139</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -913,7 +913,7 @@
         <v>46089</v>
       </c>
       <c r="C60">
-        <v>3144</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -921,7 +921,7 @@
         <v>46090</v>
       </c>
       <c r="C61">
-        <v>3406</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -929,7 +929,7 @@
         <v>46091</v>
       </c>
       <c r="C62">
-        <v>3638</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -937,7 +937,7 @@
         <v>46092</v>
       </c>
       <c r="C63">
-        <v>3727</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -948,7 +948,7 @@
         <v>1010</v>
       </c>
       <c r="C64">
-        <v>3702</v>
+        <v>3602</v>
       </c>
     </row>
   </sheetData>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5cbc24d1a217bff/Poker/Bankroll/stang-gang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FF460D1-3C78-41D7-BAF1-E4C659C50073}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1B77B6A-1DAC-4141-B8D4-5ED1A201FE78}"/>
   <bookViews>
-    <workbookView xWindow="4668" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A52CD65-A2BF-4AC2-8075-EA939B042110}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -951,6 +951,172 @@
         <v>3602</v>
       </c>
     </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C65">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>46095</v>
+      </c>
+      <c r="C66">
+        <v>4398</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>46096</v>
+      </c>
+      <c r="C67">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C68">
+        <v>4269</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C69">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C70">
+        <v>4458</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C71">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C72">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B73">
+        <v>1079</v>
+      </c>
+      <c r="C73">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>46104</v>
+      </c>
+      <c r="C74">
+        <v>4484</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C75">
+        <v>4474</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C76">
+        <v>4686</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C77">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C78">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C79">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>46110</v>
+      </c>
+      <c r="C80">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>46111</v>
+      </c>
+      <c r="C81">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C82">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B83">
+        <v>1139</v>
+      </c>
+      <c r="C83">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C84">
+        <v>4304</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5cbc24d1a217bff/Poker/Bankroll/stang-gang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1B77B6A-1DAC-4141-B8D4-5ED1A201FE78}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FABF5127-4A5D-4FEF-8798-1E63696F2633}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
+    <workbookView xWindow="3348" yWindow="2916" windowWidth="17280" windowHeight="9960" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -956,7 +956,7 @@
         <v>46094</v>
       </c>
       <c r="C65">
-        <v>3955</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -964,7 +964,7 @@
         <v>46095</v>
       </c>
       <c r="C66">
-        <v>4398</v>
+        <v>4298</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -972,7 +972,7 @@
         <v>46096</v>
       </c>
       <c r="C67">
-        <v>4218</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -980,7 +980,7 @@
         <v>46097</v>
       </c>
       <c r="C68">
-        <v>4269</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -988,7 +988,7 @@
         <v>46098</v>
       </c>
       <c r="C69">
-        <v>4106</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -996,7 +996,7 @@
         <v>46099</v>
       </c>
       <c r="C70">
-        <v>4458</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1004,7 +1004,7 @@
         <v>46100</v>
       </c>
       <c r="C71">
-        <v>4251</v>
+        <v>4151</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1012,7 +1012,7 @@
         <v>46101</v>
       </c>
       <c r="C72">
-        <v>4249</v>
+        <v>4149</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1023,7 +1023,7 @@
         <v>1079</v>
       </c>
       <c r="C73">
-        <v>3956</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -1031,7 +1031,7 @@
         <v>46104</v>
       </c>
       <c r="C74">
-        <v>4484</v>
+        <v>4384</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -1039,7 +1039,7 @@
         <v>46105</v>
       </c>
       <c r="C75">
-        <v>4474</v>
+        <v>4374</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -1047,7 +1047,7 @@
         <v>46106</v>
       </c>
       <c r="C76">
-        <v>4686</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1055,7 +1055,7 @@
         <v>46107</v>
       </c>
       <c r="C77">
-        <v>4408</v>
+        <v>4308</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1063,7 +1063,7 @@
         <v>46108</v>
       </c>
       <c r="C78">
-        <v>3970</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -1071,7 +1071,7 @@
         <v>46109</v>
       </c>
       <c r="C79">
-        <v>3905</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -1079,7 +1079,7 @@
         <v>46110</v>
       </c>
       <c r="C80">
-        <v>4435</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -1087,7 +1087,7 @@
         <v>46111</v>
       </c>
       <c r="C81">
-        <v>3998</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -1095,7 +1095,7 @@
         <v>46112</v>
       </c>
       <c r="C82">
-        <v>3717</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -1106,7 +1106,7 @@
         <v>1139</v>
       </c>
       <c r="C83">
-        <v>4104</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -1114,7 +1114,7 @@
         <v>46114</v>
       </c>
       <c r="C84">
-        <v>4304</v>
+        <v>4204</v>
       </c>
     </row>
   </sheetData>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5cbc24d1a217bff/Poker/Bankroll/stang-gang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FABF5127-4A5D-4FEF-8798-1E63696F2633}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F6CE7F5-9D5C-4344-AF75-E28A991B14AD}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="2916" windowWidth="17280" windowHeight="9960" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
+    <workbookView xWindow="2760" yWindow="3024" windowWidth="17280" windowHeight="9960" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,10 +98,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -421,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A52CD65-A2BF-4AC2-8075-EA939B042110}">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1117,6 +1113,137 @@
         <v>4204</v>
       </c>
     </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>46115</v>
+      </c>
+      <c r="C85">
+        <v>4883</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C86">
+        <v>5339</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>46117</v>
+      </c>
+      <c r="C87">
+        <v>5563</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>46118</v>
+      </c>
+      <c r="C88">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C89">
+        <v>5666</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>46120</v>
+      </c>
+      <c r="C90">
+        <v>5701</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>46121</v>
+      </c>
+      <c r="C91">
+        <v>5508</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>46122</v>
+      </c>
+      <c r="C92">
+        <v>5276</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>46124</v>
+      </c>
+      <c r="C93">
+        <v>4817</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>46125</v>
+      </c>
+      <c r="C94">
+        <v>4794</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>46126</v>
+      </c>
+      <c r="C95">
+        <v>4330</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>46127</v>
+      </c>
+      <c r="C96">
+        <v>3926</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>46131</v>
+      </c>
+      <c r="C97">
+        <v>4354</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>46132</v>
+      </c>
+      <c r="C98">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>46133</v>
+      </c>
+      <c r="C99">
+        <v>4496</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B100">
+        <v>1219</v>
+      </c>
+      <c r="C100">
+        <v>4512</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5cbc24d1a217bff/Poker/Bankroll/stang-gang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F6CE7F5-9D5C-4344-AF75-E28A991B14AD}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{DC165FDB-1FC4-4119-81A5-A298CFEEDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E776BA4F-012E-4D41-AE05-6A1F624CA4A8}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="3024" windowWidth="17280" windowHeight="9960" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{A7134671-C15C-4531-A6D4-3327DA0B4BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -98,6 +101,90 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Balance History"/>
+      <sheetName val="Tx History"/>
+      <sheetName val="Tourney History"/>
+      <sheetName val="Intra-Bankroll Tx (Untracked)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="103">
+          <cell r="B103">
+            <v>4146</v>
+          </cell>
+          <cell r="G103">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="B104">
+            <v>4055</v>
+          </cell>
+          <cell r="G104">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="B105">
+            <v>4044</v>
+          </cell>
+          <cell r="G105">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="B106">
+            <v>3604</v>
+          </cell>
+          <cell r="G106">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="B107">
+            <v>3787</v>
+          </cell>
+          <cell r="G107">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="B108">
+            <v>3868</v>
+          </cell>
+          <cell r="G108">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="B109">
+            <v>4014</v>
+          </cell>
+          <cell r="G109">
+            <v>500</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A52CD65-A2BF-4AC2-8075-EA939B042110}">
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -1241,7 +1328,74 @@
         <v>1219</v>
       </c>
       <c r="C100">
-        <v>4512</v>
+        <v>4613</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>46135</v>
+      </c>
+      <c r="C101">
+        <f>'[1]Balance History'!$B103+'[1]Balance History'!$G103</f>
+        <v>4646</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>46136</v>
+      </c>
+      <c r="C102">
+        <f>'[1]Balance History'!$B104+'[1]Balance History'!$G104</f>
+        <v>4555</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>46136</v>
+      </c>
+      <c r="C103">
+        <f>'[1]Balance History'!$B105+'[1]Balance History'!$G105</f>
+        <v>4544</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>46138</v>
+      </c>
+      <c r="C104">
+        <f>'[1]Balance History'!$B106+'[1]Balance History'!$G106</f>
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>46139</v>
+      </c>
+      <c r="C105">
+        <f>'[1]Balance History'!$B107+'[1]Balance History'!$G107</f>
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>46140</v>
+      </c>
+      <c r="C106">
+        <f>'[1]Balance History'!$B108+'[1]Balance History'!$G108</f>
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B107">
+        <f>B100+70</f>
+        <v>1289</v>
+      </c>
+      <c r="C107">
+        <f>'[1]Balance History'!$B109+'[1]Balance History'!$G109</f>
+        <v>4514</v>
       </c>
     </row>
   </sheetData>
